--- a/output/pdf_financials_xlsx/FT.xlsx
+++ b/output/pdf_financials_xlsx/FT.xlsx
@@ -5511,16 +5511,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-10.315094</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-13.975717</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-4.197126</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.5626640000000001</v>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
@@ -12882,7 +12882,11 @@
           <t>Increase in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>-10.315094</v>
       </c>
